--- a/メモYYYYMMDD.xlsx
+++ b/メモYYYYMMDD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asakuno tomohiro\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:11_{68841876-F043-49BA-931E-F85C64B1F221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:11_{C168B9CF-8F71-4A6F-8A28-ADA399D03456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="4725" windowWidth="24420" windowHeight="14445" activeTab="2" xr2:uid="{FBFCF79F-DE18-4D55-8CFC-5B607FD0DB33}"/>
+    <workbookView xWindow="3945" yWindow="1035" windowWidth="28425" windowHeight="18885" activeTab="2" xr2:uid="{FBFCF79F-DE18-4D55-8CFC-5B607FD0DB33}"/>
   </bookViews>
   <sheets>
     <sheet name="雛形" sheetId="6" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="163">
   <si>
     <t>No</t>
     <phoneticPr fontId="6"/>
@@ -1093,6 +1093,18 @@
     <rPh sb="0" eb="2">
       <t>チョウフク</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MS-Office</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>msconfig</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>AutoHotKey</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1320,7 +1332,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1396,6 +1408,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyProtection="1">
       <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -8039,15 +8054,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>609599</xdr:colOff>
-      <xdr:row>303</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:colOff>571499</xdr:colOff>
+      <xdr:row>301</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>307</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>305</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8062,7 +8077,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14325599" y="72266175"/>
+          <a:off x="14287499" y="71847075"/>
           <a:ext cx="3629026" cy="857250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8167,9 +8182,9 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>305</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>303</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
@@ -8193,8 +8208,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1" flipV="1">
-          <a:off x="17954625" y="72694800"/>
-          <a:ext cx="2809874" cy="204788"/>
+          <a:off x="17916525" y="72275700"/>
+          <a:ext cx="2847974" cy="623888"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -8343,6 +8358,2189 @@
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400">
             <a:latin typeface="+mj-ea"/>
             <a:ea typeface="+mj-ea"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>299</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>316</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="77" name="図 76">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F5EDC34C-4164-4387-97E1-8C56A5A0F0BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId53">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="71199375"/>
+          <a:ext cx="6324600" cy="4162425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>299</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>316</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="76" name="図 75">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15352781-C9CC-45DB-B98C-9FAF8FE855E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId54">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6858000" y="71199375"/>
+          <a:ext cx="6315075" cy="4152900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>304</xdr:row>
+      <xdr:rowOff>123826</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>306</xdr:row>
+      <xdr:rowOff>161926</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="88" name="線吹き出し 2 (枠付き) 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2997F8B4-8F57-4B33-B64C-FC5A28351509}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10287000" y="72513826"/>
+          <a:ext cx="2009775" cy="514350"/>
+        </a:xfrm>
+        <a:prstGeom prst="borderCallout2">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 31845"/>
+            <a:gd name="adj2" fmla="val -6250"/>
+            <a:gd name="adj3" fmla="val 86659"/>
+            <a:gd name="adj4" fmla="val -18672"/>
+            <a:gd name="adj5" fmla="val 157740"/>
+            <a:gd name="adj6" fmla="val -27988"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+              <a:latin typeface="+mj-ea"/>
+              <a:ea typeface="+mj-ea"/>
+            </a:rPr>
+            <a:t>日本語入力に必要。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>305</xdr:row>
+      <xdr:rowOff>200026</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>308</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="89" name="線吹き出し 2 (枠付き) 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E52664E-CD6C-482A-9A41-B7B180E151CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3495675" y="72828151"/>
+          <a:ext cx="2009775" cy="514350"/>
+        </a:xfrm>
+        <a:prstGeom prst="borderCallout2">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 31845"/>
+            <a:gd name="adj2" fmla="val -6250"/>
+            <a:gd name="adj3" fmla="val 86659"/>
+            <a:gd name="adj4" fmla="val -18672"/>
+            <a:gd name="adj5" fmla="val 157740"/>
+            <a:gd name="adj6" fmla="val -27988"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200">
+              <a:latin typeface="+mj-ea"/>
+              <a:ea typeface="+mj-ea"/>
+            </a:rPr>
+            <a:t>MS-Office</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200">
+              <a:latin typeface="+mj-ea"/>
+              <a:ea typeface="+mj-ea"/>
+            </a:rPr>
+            <a:t>起動に必要。</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>320</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>343</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="78" name="図 77">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F62FA673-5863-4D72-977F-B7DE6DF368C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId55">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="76200000"/>
+          <a:ext cx="7477125" cy="5667375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>319</xdr:row>
+      <xdr:rowOff>238124</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>346</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="80" name="テキスト ボックス 79">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC2646BF-D69C-4AE8-B31D-33494F2904DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6858000" y="76199999"/>
+          <a:ext cx="7543800" cy="6191251"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>■以下</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>ホットキー</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Win</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>キー＋標準キー</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>c	googleChrome</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>ブラウザ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>(※)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			f	Firefox</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>ブラウザ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>(※)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			g	Git(Sourcetree)(※)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			h	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>秀丸エディタ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>(※)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			k	Slack(chat)(※)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			p	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>ペイント</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>(※)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			v	Gvim</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>エディタ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>(※)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>	Win</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>キー </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>+ Ctrl</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>キー </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>標準キー</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>j	Jasper soft</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			s	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>サクラエディタ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>(※)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>	Win</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>キー </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>+ Alt</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>キー </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>標準キー</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>r</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			c	Discord(chat)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			e	Evernote</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			i	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>一太郎</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>j	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>ジャストシステムのツールとユーティリティ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>k	Kindle</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			m	minecraft</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			n	Notepad++</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			o	Origin Game</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			s	Steam Game</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			t	calc(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>計算ソフトウェア</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			w	JW_CAD</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			x	Dropbox</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>	Win</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>キー </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>+ Alt</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>キー </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>+ Shift + </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>標準キー</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Win</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>キー </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>+ Alt</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>キー </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>+ Ctrl</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>キー </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>標準キー</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>エクスプローラ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Win</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>キー </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>+ Ctrl</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>キー </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>標準キー</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>e	Explorer</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>をすべてアクティブにする。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>x	Explorer</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>をすべてアクティブにする</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>(dropbox</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>以外</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Win</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>キー </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>+ Shift</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>キー </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>標準キー</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>e	Explorer</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>をすべて最小化にする。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>x	Explorer</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>を順次アクティブにする</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>(dropbox</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>のみ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>アプリケーションキーとの組み合わせ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>AppsKey + </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>標準キー</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>Pause + </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>標準キー</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>F1 + </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>標準キー</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>a	Access	※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>切り替えがうまくいかず。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>b	Blend(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>廃止予定</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)	※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>切り替えが全くうまくいかず。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>d	Delve(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>設定無し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			d	OneDrive</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			e	Excel</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>アクティブ化</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>f	Forms(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>設定無し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			g	Groove(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>廃止</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>共同作業ツール</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>h	Publisher("</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>版元</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>"</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>の頭文字</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>個人出版用ツール？	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>切り替えがうまくいかず。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>i	IDE(VisualStudio)	※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>切り替えがうまくいかず。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>i	InfoPath(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>廃止</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			k	Kaizala(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>設定無し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			k	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>スクリーンキーボード</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>l	Excel</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>新規起動</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>l	Microsoft Lists(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>設定無し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			m	Outlook</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			n	OneNote</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			p	Planner(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>設定無し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			p	PowerPoint</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			p	Project(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>設定無し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			s	PowerShell</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			s	SharePoint(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>設定無し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			s	Skype(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>設定無し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			s	Stream(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>設定無し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			s	Sway(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>設定無し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			t	Microsoft Teams(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>設定無し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			t	To-Do(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>設定無し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			t	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>タスクマネージャ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u	</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>電卓</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>v	Visio(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>設定無し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			v	Visual Studio Code</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			w	Whiteboard(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>設定無し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			w	Word</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			y	Yammer(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>設定無し</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>ポウズキー</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>(Pause)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>との組み合わせ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>上記</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>MS-Office</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>起動対応</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			i	IDE(Eclipse)	※</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>起動させられない。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>F10</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>との組み合わせ</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>u	Bash on Ubuntu</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			o	Oxygen Not Included</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>			f	Factorio</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>※WindowOS</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+              <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+              <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            </a:rPr>
+            <a:t>標準のショートカットキーを上書きすることになるため、気をつけること。</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
+            <a:latin typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
+            <a:ea typeface="ＭＳ ゴシック" panose="020B0609070205080204" pitchFamily="49" charset="-128"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -12927,7 +15125,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AL295"/>
+  <dimension ref="A1:AL320"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.4">
@@ -13411,12 +15609,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="291" spans="4:9" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.4">
       <c r="D291" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="292" spans="4:9" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.4">
       <c r="E292" s="17" t="s">
         <v>102</v>
       </c>
@@ -13427,7 +15625,7 @@
       </c>
       <c r="I292" s="19"/>
     </row>
-    <row r="293" spans="4:9" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.4">
       <c r="E293" s="17" t="s">
         <v>103</v>
       </c>
@@ -13438,7 +15636,7 @@
       </c>
       <c r="I293" s="19"/>
     </row>
-    <row r="294" spans="4:9" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.4">
       <c r="E294" s="17" t="s">
         <v>105</v>
       </c>
@@ -13449,7 +15647,7 @@
       </c>
       <c r="I294" s="19"/>
     </row>
-    <row r="295" spans="4:9" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.4">
       <c r="E295" s="17" t="s">
         <v>106</v>
       </c>
@@ -13459,6 +15657,21 @@
         <v>110</v>
       </c>
       <c r="I295" s="19"/>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A299" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="B300" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.4">
+      <c r="A320" s="28" t="s">
+        <v>162</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
@@ -13469,9 +15682,10 @@
     <hyperlink ref="T83" r:id="rId4" xr:uid="{DE0CA062-E075-4E9F-B2FF-C7119096B9E1}"/>
     <hyperlink ref="Y124" r:id="rId5" xr:uid="{6C17AB30-7729-4D3C-BCAD-C46426245979}"/>
     <hyperlink ref="O18" r:id="rId6" xr:uid="{94A068EE-CAA7-4943-A7A3-745917590CC7}"/>
+    <hyperlink ref="A320" r:id="rId7" xr:uid="{23EEBEA9-153F-4A4A-860D-063ABBA7181E}"/>
   </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="22" fitToHeight="0" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" scale="22" fitToHeight="0" orientation="portrait" r:id="rId8"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;Z&amp;F&amp;R
 シート名：&amp;A</oddHeader>
@@ -13480,6 +15694,6 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="179" max="39" man="1"/>
   </rowBreaks>
-  <drawing r:id="rId8"/>
+  <drawing r:id="rId9"/>
 </worksheet>
 </file>